--- a/AmericanSelect_ProfitabilityReport.xlsx
+++ b/AmericanSelect_ProfitabilityReport.xlsx
@@ -1,16 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68603F39-C80C-40E8-88FF-B34C76CF622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Best Performers" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Loss-Makers &amp; Fixes" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Action Plan" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Vendor Breakdown" state="visible" r:id="rId8"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Best Performers" sheetId="2" r:id="rId2"/>
+    <sheet name="Loss-Makers &amp; Fixes" sheetId="3" r:id="rId3"/>
+    <sheet name="Action Plan" sheetId="4" r:id="rId4"/>
+    <sheet name="Vendor Breakdown" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -785,91 +794,117 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="#,##0 &quot;FCFA&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0\ &quot;FCFA&quot;"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFD4AF37"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF888888"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFD4AF37"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFD4AF37"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFD4AF37"/>
-      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF888888"/>
       <sz val="11"/>
+      <color rgb="FFCC0000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFD4AF37"/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFD4AF37"/>
       <sz val="11"/>
+      <color rgb="FFCC0000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFE65100"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF2E7D32"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <color rgb="FF1A1A1A"/>
-    </font>
-    <font>
-      <color rgb="FF2E7D32"/>
+      <color rgb="FFD4AF37"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFD4AF37"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF2E7D32"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FFCC0000"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFCC0000"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFE65100"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFD4AF37"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF1565C0"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="12">
@@ -971,15 +1006,6 @@
   </cellStyleXfs>
   <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1020,109 +1046,118 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1463,355 +1498,357 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="5" width="20" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="52.28515625" customWidth="1"/>
+    <col min="5" max="5" width="59.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+    </row>
+    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+    </row>
+    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="13" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="8">
         <v>289</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="9">
         <v>1759000</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="11">
         <v>206</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="12">
         <v>1225600</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="8">
         <v>130</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="9">
         <v>1040500</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="11">
         <v>152</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="12">
         <v>736500</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="8">
         <v>45</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="13">
         <v>357000</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="11">
         <v>42</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="14">
         <v>321500</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="8">
         <v>47</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="13">
         <v>290500</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+    <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="11">
         <v>19</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="14">
         <v>108000</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+    <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="8">
         <v>7</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="13">
         <v>59500</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+    <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="16">
         <v>967</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="16">
         <v>6155600</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1823,14 +1860,14 @@
     <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1839,268 +1876,268 @@
     <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="2" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="18" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="21" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="18" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="21" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="21" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2109,14 +2146,14 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2125,244 +2162,244 @@
     <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-    </row>
-    <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+    </row>
+    <row r="3" spans="1:6" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="23" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="27" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="27" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="27" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="27" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="27" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="32" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="32" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="32" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="32" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="32" t="s">
         <v>176</v>
       </c>
     </row>
@@ -2372,14 +2409,14 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2388,166 +2425,166 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+    </row>
+    <row r="2" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+    <row r="4" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="35" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+    <row r="5" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="E5" s="45" t="s">
+      <c r="E5" s="39" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+    <row r="6" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="35" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+    <row r="7" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="E7" s="45" t="s">
+      <c r="E7" s="39" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+    <row r="8" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="35" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+    <row r="9" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="E9" s="45" t="s">
+      <c r="E9" s="39" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
+    <row r="10" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="35" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
+    <row r="11" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="E11" s="45" t="s">
+      <c r="E11" s="39" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2556,316 +2593,316 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="52" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="2" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C4" s="45">
         <v>636</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="46">
         <v>381600</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="7" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="C5" s="53">
+      <c r="C5" s="47">
         <v>839</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="48">
         <v>503400</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="10" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="45">
         <v>1050</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="46">
         <v>630000</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="7" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="47">
         <v>248</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="48">
         <v>148800</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="10" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="45">
         <v>321</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="46">
         <v>192600</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="7" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="47">
         <v>264</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="48">
         <v>158400</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="10" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="45">
         <v>251</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="46">
         <v>150600</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="7" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="53">
+      <c r="C11" s="47">
         <v>208</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="48">
         <v>124800</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="45">
         <v>143</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="46">
         <v>85800</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C13" s="53">
+      <c r="C13" s="47">
         <v>137</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="48">
         <v>82200</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="10" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="45">
         <v>63</v>
       </c>
-      <c r="D14" s="52">
+      <c r="D14" s="46">
         <v>37800</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="7" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="C15" s="53">
+      <c r="C15" s="47">
         <v>53</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="48">
         <v>31800</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="10" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="51">
+      <c r="C16" s="45">
         <v>70</v>
       </c>
-      <c r="D16" s="52">
+      <c r="D16" s="46">
         <v>42000</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="7" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="47">
         <v>58</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="48">
         <v>34800</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="10" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C18" s="51">
+      <c r="C18" s="45">
         <v>168</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="46">
         <v>100800</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="7" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="15" t="s">
         <v>254</v>
       </c>
     </row>
@@ -2874,6 +2911,6 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>